--- a/downloads_generacion/extracted_precios_c_iny_0923.xlsx
+++ b/downloads_generacion/extracted_precios_c_iny_0923.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENTE</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
